--- a/astro-site/public/dl/kit-tareas-pizzeria/08-apertura-cierre-negocio.xlsx
+++ b/astro-site/public/dl/kit-tareas-pizzeria/08-apertura-cierre-negocio.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Apertura del Negocio" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cierre del Negocio" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura del Negocio" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre del Negocio" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Area">'Instrucciones'!$A$1:$A$20</definedName>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Apertura del Negocio'!$A$1:$H$24</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Cierre del Negocio'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$A$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura del Negocio'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre del Negocio'!$A$1:$H$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,6 +76,11 @@
       <i val="1"/>
       <color rgb="00888888"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -140,51 +145,62 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -544,122 +560,131 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="80"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="40" r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>AI Chef Pro — aichef.pro</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="30" r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Kit de Tareas — Pizzería</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="25" r="3">
+    <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Checklist de Apertura y Cierre del Negocio</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="35" r="5">
+    <row r="4"/>
+    <row r="5" ht="35" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>📋 Instrucciones de Uso</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>1. Este archivo contiene checklists profesionales para la apertura y cierre de tu negocio.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2. Imprime las hojas que necesites o úsalas en formato digital (tablet/ordenador).</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>3. Cada checklist incluye columnas para marcar tareas completadas, responsable, hora y notas.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>4. Personaliza las tareas según las necesidades específicas de tu establecimiento.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="10">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>5. Añade o elimina filas según tu operativa diaria.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="11">
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>6. Usa la validación de datos en la columna '✓ Completada' para marcar el estado.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="12">
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>7. Rellena la firma y fecha cada día para mantener el control.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="13">
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" s="5" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="14">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>💡 Consejo: Plastifica una copia impresa y usa rotuladores borrables para reutilizarla cada día.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="15">
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" s="5" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="16">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>© AI Chef Pro — aichef.pro</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="17">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>29 años de experiencia en alta hostelería · 15 años de consultoría gastronómica</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="18">
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pizzeria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -667,7 +692,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -681,24 +715,24 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="50"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="13"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="25"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="40" r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Apertura del Negocio — Pizzería</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="28" r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Fecha: ____/____/________</t>
@@ -710,8 +744,8 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="8" r="3"/>
-    <row customHeight="1" ht="28" r="4">
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>#</t>
@@ -753,7 +787,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="24" r="5">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
@@ -773,7 +807,7 @@
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="6">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
@@ -793,7 +827,7 @@
       <c r="G6" s="10" t="inlineStr"/>
       <c r="H6" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="7">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
@@ -813,7 +847,7 @@
       <c r="G7" s="8" t="inlineStr"/>
       <c r="H7" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="8">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
@@ -833,7 +867,7 @@
       <c r="G8" s="10" t="inlineStr"/>
       <c r="H8" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="9">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
@@ -853,7 +887,7 @@
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="10">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="10" t="n">
         <v>6</v>
       </c>
@@ -873,7 +907,7 @@
       <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="11">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
@@ -893,7 +927,7 @@
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="12">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
@@ -913,7 +947,7 @@
       <c r="G12" s="10" t="inlineStr"/>
       <c r="H12" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="13">
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
@@ -933,7 +967,7 @@
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="14">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
@@ -953,7 +987,7 @@
       <c r="G14" s="10" t="inlineStr"/>
       <c r="H14" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="15">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
@@ -973,7 +1007,7 @@
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="16">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>12</v>
       </c>
@@ -993,7 +1027,7 @@
       <c r="G16" s="10" t="inlineStr"/>
       <c r="H16" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="17">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="8" t="n">
         <v>13</v>
       </c>
@@ -1013,7 +1047,7 @@
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="18">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="10" t="n">
         <v>14</v>
       </c>
@@ -1033,7 +1067,7 @@
       <c r="G18" s="10" t="inlineStr"/>
       <c r="H18" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="19">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="8" t="n">
         <v>15</v>
       </c>
@@ -1053,7 +1087,7 @@
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="20">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="10" t="n">
         <v>16</v>
       </c>
@@ -1073,7 +1107,7 @@
       <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="21">
+    <row r="21" ht="24" customHeight="1">
       <c r="A21" s="8" t="n">
         <v>17</v>
       </c>
@@ -1093,7 +1127,27 @@
       <c r="G21" s="8" t="inlineStr"/>
       <c r="H21" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="30" r="23">
+    <row r="22">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C22">
+        <f>COUNTIF(F5:F21,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E22">
+        <f>COUNTIF(B5:B21,"?*")</f>
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora de finalización: ________</t>
@@ -1115,13 +1169,18 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A23:H23"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:H21">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Selecciona ✓, ✗ o —" errorTitle="Valor no válido" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1135,24 +1194,24 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="50"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="13"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="25"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="40" r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cierre del Negocio — Pizzería</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="28" r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Fecha: ____/____/________</t>
@@ -1164,8 +1223,8 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="8" r="3"/>
-    <row customHeight="1" ht="28" r="4">
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>#</t>
@@ -1207,7 +1266,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="24" r="5">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
@@ -1227,7 +1286,7 @@
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="6">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
@@ -1247,7 +1306,7 @@
       <c r="G6" s="10" t="inlineStr"/>
       <c r="H6" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="7">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
@@ -1267,7 +1326,7 @@
       <c r="G7" s="8" t="inlineStr"/>
       <c r="H7" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="8">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
@@ -1287,7 +1346,7 @@
       <c r="G8" s="10" t="inlineStr"/>
       <c r="H8" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="9">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
@@ -1307,7 +1366,7 @@
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="10">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="10" t="n">
         <v>6</v>
       </c>
@@ -1327,7 +1386,7 @@
       <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="11">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
@@ -1347,7 +1406,7 @@
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="12">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
@@ -1367,7 +1426,7 @@
       <c r="G12" s="10" t="inlineStr"/>
       <c r="H12" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="13">
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
@@ -1387,7 +1446,7 @@
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="14">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
@@ -1407,7 +1466,7 @@
       <c r="G14" s="10" t="inlineStr"/>
       <c r="H14" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="15">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
@@ -1427,7 +1486,7 @@
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="16">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>12</v>
       </c>
@@ -1447,7 +1506,7 @@
       <c r="G16" s="10" t="inlineStr"/>
       <c r="H16" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="17">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="8" t="n">
         <v>13</v>
       </c>
@@ -1467,7 +1526,7 @@
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="18">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="10" t="n">
         <v>14</v>
       </c>
@@ -1487,7 +1546,27 @@
       <c r="G18" s="10" t="inlineStr"/>
       <c r="H18" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="30" r="20">
+    <row r="19">
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C19">
+        <f>COUNTIF(F5:F18,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E19">
+        <f>COUNTIF(B5:B18,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora de finalización: ________</t>
@@ -1509,12 +1588,17 @@
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:H18">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Selecciona ✓, ✗ o —" errorTitle="Valor no válido" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18" type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pizzeria/08-apertura-cierre-negocio.xlsx
+++ b/astro-site/public/dl/kit-tareas-pizzeria/08-apertura-cierre-negocio.xlsx
@@ -13,7 +13,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$A$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura del Negocio'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura del Negocio'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cierre del Negocio'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre del Negocio'!$A$1:$H$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -710,7 +712,7 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
@@ -1179,8 +1181,16 @@
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1189,7 +1199,7 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
@@ -1598,7 +1608,15 @@
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pizzeria/08-apertura-cierre-negocio.xlsx
+++ b/astro-site/public/dl/kit-tareas-pizzeria/08-apertura-cierre-negocio.xlsx
@@ -12,11 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre del Negocio" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$A$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura del Negocio'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura del Negocio'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura del Negocio'!$A$1:$H$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cierre del Negocio'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre del Negocio'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre del Negocio'!$A$1:$H$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,8 +84,22 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -122,6 +136,11 @@
         <bgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -149,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -188,6 +207,39 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -564,136 +616,252 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AI Chef Pro — aichef.pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Kit de Tareas — Pizzería</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Checklist de Apertura y Cierre del Negocio</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>📋 Instrucciones de Uso</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>1. Este archivo contiene checklists profesionales para la apertura y cierre de tu negocio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2. Imprime las hojas que necesites o úsalas en formato digital (tablet/ordenador).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>3. Cada checklist incluye columnas para marcar tareas completadas, responsable, hora y notas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>4. Personaliza las tareas según las necesidades específicas de tu establecimiento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>5. Añade o elimina filas según tu operativa diaria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>6. Usa la validación de datos en la columna '✓ Completada' para marcar el estado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>7. Rellena la firma y fecha cada día para mantener el control.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>💡 Consejo: Plastifica una copia impresa y usa rotuladores borrables para reutilizarla cada día.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>© AI Chef Pro — aichef.pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Apertura y Cierre del Negocio — Pizzería</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Qué resuelve</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>▸ Es el checklist del LOCAL COMPLETO: lo que se abre y se cierra del negocio entero, no de cada área. Úsalo como marco del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>▸ El detalle por área (cocina, sala) va en 01-apertura-cierre.xlsx: no repitas el trabajo, cada fichero cubre un nivel distinto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Cómo usar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>▸ Imprime la hoja del turno (apertura o cierre) o úsala en tablet; el responsable reparte y cada persona firma su tarea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>▸ Cada tarea trae Responsable y Hora Límite precargados con el criterio del kit: ajústalos a tu horario real, son celdas verdes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Celdas editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>▸ Todo lo que se rellena a diario va en VERDE: Responsable, Hora Límite, ✓ Completada, Firma y Notas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1">
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1">
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>▸ Estás en 08-apertura-cierre-negocio.xlsx: este ES el marco del día — el HITO de abrir y cerrar el local; el DETALLE de cada zona está en 01-apertura-cierre.xlsx y el DINERO, en 09-apertura-cierre-caja.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Pizzería · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="35" customHeight="1">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>Contacto: info@aichef.pro</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pizzeria · info@aichef.pro</t>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pizzeria · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1"/>
-  </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -714,7 +882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -790,399 +958,588 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Desactivar alarma del local</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="9" t="inlineStr"/>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr"/>
+      <c r="G5" s="19" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Encender luces generales (interior y exterior)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="11" t="inlineStr"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr"/>
+      <c r="G6" s="19" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Encender climatización (HVAC) / calefacción según temporada</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="19" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Abrir persianas / puerta principal</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr"/>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="10" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr"/>
-      <c r="H8" s="11" t="inlineStr"/>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Montar señalización exterior / pizarra de menú</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Exterior</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Encender TPV / POS / datáfono</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>Caja</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="10" t="inlineStr"/>
-      <c r="G10" s="10" t="inlineStr"/>
-      <c r="H10" s="11" t="inlineStr"/>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Encender sistema de reservas / tablet de pedidos</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Recepción</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Poner música ambiente al volumen adecuado</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="10" t="inlineStr"/>
-      <c r="H12" s="11" t="inlineStr"/>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr"/>
+      <c r="G12" s="19" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Revisar reservas del día y eventos especiales</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Recepción</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="9" t="inlineStr"/>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr"/>
+      <c r="G13" s="19" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Comprobar baños: papel, jabón, limpieza, ambientador</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Baños</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="10" t="inlineStr"/>
-      <c r="H14" s="11" t="inlineStr"/>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr"/>
+      <c r="G14" s="19" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Verificar limpieza de zonas comunes (entrada, pasillos)</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Zonas comunes</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="10" t="n">
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr"/>
+      <c r="G15" s="19" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Revisar estado del mobiliario (sillas, mesas, iluminación)</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="10" t="inlineStr"/>
-      <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr"/>
-      <c r="H16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="8" t="n">
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr"/>
+      <c r="G16" s="19" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Montar terraza si aplica (mesas, sillas, sombrillas/estufas)</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr"/>
-      <c r="H17" s="9" t="inlineStr"/>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr"/>
+      <c r="G17" s="19" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Comprobar que las cartas/menús están en orden</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr"/>
-      <c r="E18" s="10" t="inlineStr"/>
-      <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr"/>
-      <c r="H18" s="11" t="inlineStr"/>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr"/>
+      <c r="G18" s="19" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Encender displays / pantallas informativas si las hay</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr"/>
-      <c r="H19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="10" t="n">
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr"/>
+      <c r="G19" s="19" t="inlineStr"/>
+      <c r="H19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>Encender horno de leña (precalentar 1h antes del servicio)</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="10" t="inlineStr"/>
-      <c r="F20" s="10" t="inlineStr"/>
-      <c r="G20" s="10" t="inlineStr"/>
-      <c r="H20" s="11" t="inlineStr"/>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr"/>
+      <c r="G20" s="19" t="inlineStr"/>
+      <c r="H20" s="20" t="inlineStr"/>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Montar barra de pizza si es visible</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr"/>
-      <c r="H21" s="9" t="inlineStr"/>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr"/>
+      <c r="G21" s="19" t="inlineStr"/>
+      <c r="H21" s="20" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="inlineStr">
+      <c r="A22" s="19" t="n"/>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="20" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="n"/>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="20" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="n"/>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="19" t="n"/>
+      <c r="H24" s="20" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="n"/>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="20" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="n"/>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="19" t="n"/>
+      <c r="H26" s="20" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C22">
-        <f>COUNTIF(F5:F21,"✓")</f>
+      <c r="D28">
+        <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E22">
-        <f>COUNTIF(B5:B21,"?*")</f>
+      <c r="F28">
+        <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
         <v>17.0</v>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora de finalización: ________</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>© AI Chef Pro — aichef.pro</t>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Pizzería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="6">
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H21">
+  <conditionalFormatting sqref="A5:H26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
@@ -1201,7 +1558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1257,7 +1614,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1277,339 +1634,504 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Apagar música ambiente</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="9" t="inlineStr"/>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr"/>
+      <c r="G5" s="19" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Verificar que no quedan clientes en el local</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="11" t="inlineStr"/>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr"/>
+      <c r="G6" s="19" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Limpiar y recoger terraza si aplica</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="19" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Apagar TPV / POS / datáfono (o dejar en standby)</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Caja</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr"/>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="10" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr"/>
-      <c r="H8" s="11" t="inlineStr"/>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Cerrar persianas y puertas</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Apagar luces (dejar mínimas de seguridad)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="10" t="inlineStr"/>
-      <c r="G10" s="10" t="inlineStr"/>
-      <c r="H10" s="11" t="inlineStr"/>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Apagar climatización</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Recoger señalización exterior</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>Exterior</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="10" t="inlineStr"/>
-      <c r="H12" s="11" t="inlineStr"/>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr"/>
+      <c r="G12" s="19" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Comprobar que ventanas están cerradas</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="9" t="inlineStr"/>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr"/>
+      <c r="G13" s="19" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Vaciar papeleras de zonas comunes y baños</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Baños</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="10" t="inlineStr"/>
-      <c r="H14" s="11" t="inlineStr"/>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr"/>
+      <c r="G14" s="19" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Revisión final de seguridad (gas, agua, enchufes)</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr"/>
+      <c r="G15" s="19" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Activar alarma</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="10" t="inlineStr"/>
-      <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr"/>
-      <c r="H16" s="11" t="inlineStr"/>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Último en salir</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr"/>
+      <c r="G16" s="19" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Cerrar con llave y verificar cierre</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr"/>
-      <c r="H17" s="9" t="inlineStr"/>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Último en salir</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr"/>
+      <c r="G17" s="19" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Apagar horno de leña / dejar enfriar</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr"/>
-      <c r="E18" s="10" t="inlineStr"/>
-      <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr"/>
-      <c r="H18" s="11" t="inlineStr"/>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Último en salir</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr"/>
+      <c r="G18" s="19" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="13" t="inlineStr">
+      <c r="A19" s="19" t="n"/>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="20" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="n"/>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="20" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="n"/>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="20" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="n"/>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="20" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="n"/>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="20" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C19">
-        <f>COUNTIF(F5:F18,"✓")</f>
+      <c r="D25">
+        <f>COUNTIFS(B5:B23,"?*",F5:F23,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E19">
-        <f>COUNTIF(B5:B18,"?*")</f>
+      <c r="F25">
+        <f>COUNTIF(B5:B23,"?*")-COUNTIF(F5:F23,"N/A")</f>
         <v>14.0</v>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora de finalización: ________</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>© AI Chef Pro — aichef.pro</t>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Pizzería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="6">
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H18">
+  <conditionalFormatting sqref="A5:H23">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
